--- a/data/use/InputData.xlsx
+++ b/data/use/InputData.xlsx
@@ -18978,7 +18978,7 @@
         <v>43282</v>
       </c>
       <c r="F617">
-        <v>971.2000000000001</v>
+        <v>971.2</v>
       </c>
       <c r="G617" t="inlineStr">
         <is>
@@ -19110,7 +19110,7 @@
         <v>42917</v>
       </c>
       <c r="F621">
-        <v>963.2000000000001</v>
+        <v>963.2</v>
       </c>
       <c r="G621" t="inlineStr">
         <is>
@@ -19242,7 +19242,7 @@
         <v>42552</v>
       </c>
       <c r="F625">
-        <v>919.7000000000001</v>
+        <v>919.7</v>
       </c>
       <c r="G625" t="inlineStr">
         <is>
@@ -19374,7 +19374,7 @@
         <v>42186</v>
       </c>
       <c r="F629">
-        <v>885.2000000000001</v>
+        <v>885.2</v>
       </c>
       <c r="G629" t="inlineStr">
         <is>
@@ -19407,7 +19407,7 @@
         <v>42095</v>
       </c>
       <c r="F630">
-        <v>885.7000000000001</v>
+        <v>885.7</v>
       </c>
       <c r="G630" t="inlineStr">
         <is>
@@ -19803,7 +19803,7 @@
         <v>41000</v>
       </c>
       <c r="F642">
-        <v>874.2000000000001</v>
+        <v>874.2</v>
       </c>
       <c r="G642" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>40909</v>
       </c>
       <c r="F643">
-        <v>883.7000000000001</v>
+        <v>883.7</v>
       </c>
       <c r="G643" t="inlineStr">
         <is>
@@ -19869,7 +19869,7 @@
         <v>40817</v>
       </c>
       <c r="F644">
-        <v>957.2000000000001</v>
+        <v>957.2</v>
       </c>
       <c r="G644" t="inlineStr">
         <is>
@@ -19968,7 +19968,7 @@
         <v>40544</v>
       </c>
       <c r="F647">
-        <v>916.7000000000001</v>
+        <v>916.7</v>
       </c>
       <c r="G647" t="inlineStr">
         <is>
